--- a/FieldConfigrationFile.xlsx
+++ b/FieldConfigrationFile.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\I\Email\AB-IMG-Rakesh\AB-IMG-Rakesh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P_Singh07\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D605C4FA-209F-4FEF-8C86-1BA82B6D4D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FD32C5A-B07C-4D86-A961-FC517DD9948D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{02CFE6FC-DC13-4DF7-B179-54CE07624848}"/>
+    <workbookView xWindow="3855" yWindow="3855" windowWidth="21600" windowHeight="11385" xr2:uid="{02CFE6FC-DC13-4DF7-B179-54CE07624848}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -423,9 +423,6 @@
 If the applicant is a Company or any other entity, mark it as Non-Individual.</t>
   </si>
   <si>
-    <t>Criticality</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
@@ -784,7 +781,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> sheet, navigate to the </t>
+      <t xml:space="preserve"> sheet of the CAM Excel, go to the </t>
     </r>
     <r>
       <rPr>
@@ -805,34 +802,55 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> section and extract the value from the field </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Loan Amount.”</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Check the “Proposed Loan Break-up” section which will be in Tabular Form  and pick the value from the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>field “Loan Amount.”</t>
+      <t xml:space="preserve"> section and pick the value from the field </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Tenure (Months).”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the tabular section titled </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Proposed Loan Break-up,”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> extract the value from the field </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Tenure (Months).”</t>
     </r>
   </si>
   <si>
@@ -858,44 +876,44 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> section, refer to the field </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Loan Amount Requested.”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Use the given value for mapping this PAS Field.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The loan amount is typically mentioned in the Email Subject, such as </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Loan Amount – 15.00 Lacs,” “19 Lacs,”</t>
+      <t xml:space="preserve"> section, use the value from the field </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Loan Tenure (Months)”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for mapping this PAS Field.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The tenure is usually mentioned in the Email Subject, such as </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“240 Months”</t>
     </r>
     <r>
       <rPr>
@@ -916,22 +934,299 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">“Rs 30.00 Lacs.”, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>etc.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the </t>
+      <t>“Tenure – 240 Months”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> etc.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the CAM Excel file, within the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Basic Input sheet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> under the Proposed Loan Breakup section, there is a</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> field called “Type of Loan.”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> This field typically contains values such as Home Loan.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>In the PD (Word document), within the Proposed Loan Breakup table, there is a</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> field  “Type of Loan.”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> This field generally includes values such as Home Loan, Composite Loan (Plot Purchase plus Home Construction), and similar options.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the Application Form, at the beginning of the document, there is a section titled </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Loan Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Under this section, you will find a field named </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Scheme,”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> which typically contains values such as </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">PLOT AND </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> HOME CONSTRUCTION LOAN,  PLOT HOME CONSTRUCTION LOAN among others.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>In the PD report, under the Applicant Details section, there is a</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> field</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> labeled “</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,” which generally contains values such as Salaried, among others.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the Application Form, under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Occupation/Business Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> section, the field </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Salaried / Self-Employed”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> typically contains values such as </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Salaried</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SENP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, and other similar categories.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the CAM file, under the </t>
     </r>
     <r>
       <rPr>
@@ -952,463 +1247,180 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> sheet of the CAM Excel, go to the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Proposed Loan Break-up”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> section and pick the value from the field </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Tenure (Months).”</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the tabular section titled </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Proposed Loan Break-up,”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> extract the value from the field </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Tenure (Months).”</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Loan Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> section, use the value from the field </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Loan Tenure (Months)”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> for mapping this PAS Field.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The tenure is usually mentioned in the Email Subject, such as </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“240 Months”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> or </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Tenure – 240 Months”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> etc.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Basic Input</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sheet under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Proposed Loan Break-up”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> section, extract the value from the field </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Proposed ROI.”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> This value is typically presented in formats like </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10.50%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> or </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>12.00% etc.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Proposed Loan Break-up” section</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> which will be tabular form, refer to the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>field name “Proposed ROI,”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> where the value will appear in formats such as 10.50% or 12.00% etc</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the CAM Excel file, within the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Basic Input sheet</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> under the Proposed Loan Breakup section, there is a</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> field called “Type of Loan.”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> This field typically contains values such as Home Loan.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>In the PD (Word document), within the Proposed Loan Breakup table, there is a</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> field  “Type of Loan.”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> This field generally includes values such as Home Loan, Composite Loan (Plot Purchase plus Home Construction), and similar options.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the Application Form, at the beginning of the document, there is a section titled </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Loan Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Under this section, you will find a field named </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Scheme,”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> which typically contains values such as </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">PLOT AND </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> HOME CONSTRUCTION LOAN,  PLOT HOME CONSTRUCTION LOAN among others.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>In the PD report, under the Applicant Details section, there is a</t>
+      <t xml:space="preserve"> sheet and the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Parties to the Loan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> section, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>the field</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Name”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> typically contains values such as </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vikram Singh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Girish Kumar Nanda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mohd. Azhar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, and similar entries.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the Application Form, under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Personal Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>section</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, the</t>
     </r>
     <r>
       <rPr>
@@ -1429,28 +1441,91 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> labeled “</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,” which generally contains values such as Salaried, among others.</t>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Name”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> will contain values such as </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vikram Singh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Girish Kumar Nanda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mohd. Azhar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, and similar applicant names.</t>
     </r>
   </si>
   <si>
@@ -1466,28 +1541,248 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Occupation/Business Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> section, the field </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Salaried / Self-Employed”</t>
+      <t>Personal Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> section, the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>field</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Date of Birth”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> usually values appears in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DD/MM/YYYY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> format, with sample values such as </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>02/01/2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>24/03/1991</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, and similar dates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the PD document, under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Applicant Details section</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>review the details of the second applicant.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> There, you will find a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>field name “Relationship”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> which typically includes values such as Spouse, Mother, and similar relationships.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the Application Form, under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Current/Communication Address</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> section, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>the field</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“City”</t>
     </r>
     <r>
       <rPr>
@@ -1508,7 +1803,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Salaried</t>
+      <t>Bhopal</t>
     </r>
     <r>
       <rPr>
@@ -1529,127 +1824,75 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>SENP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, and other similar categories.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>In the CAM file, under the AffordableCMAssessedIncome sheet, the</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> field “FOIR for Applied Loan Amount”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> typically contains values such as 44.55%, 33.24%, and similar percentages.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the PD (Word document), under the Income Details section, which contains tabular data, the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>field “FOIR for Applied Loan Amount”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> typically includes values such as 55.02%, 33.24%, and similar percentages.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the CAM file, under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Basic Input</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sheet and the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Parties to the Loan</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> section, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>the field</t>
+      <t>Indore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lucknow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, and similar city names.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the Application Form, under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Current/Communication Address</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> section,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the field</t>
     </r>
     <r>
       <rPr>
@@ -1670,7 +1913,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>“Name”</t>
+      <t>“Pincode”</t>
     </r>
     <r>
       <rPr>
@@ -1691,7 +1934,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Vikram Singh</t>
+      <t>226024</t>
     </r>
     <r>
       <rPr>
@@ -1712,7 +1955,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Girish Kumar Nanda</t>
+      <t>110024</t>
     </r>
     <r>
       <rPr>
@@ -1733,117 +1976,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Mohd. Azhar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, and similar entries.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the Application Form, under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Personal Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>section</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, the</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> field</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Name”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> will contain values such as </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Vikram Singh</t>
+      <t>201010</t>
     </r>
     <r>
       <rPr>
@@ -1864,556 +1997,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Girish Kumar Nanda</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Mohd. Azhar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, and similar applicant names.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the Application Form, under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Personal Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> section, the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>field</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Date of Birth”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> usually values appears in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DD/MM/YYYY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> format, with sample values such as </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>02/01/2024</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>24/03/1991</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, and similar dates.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the PD document, under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Applicant Details section</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>review the details of the second applicant.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> There, you will find a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>field name “Relationship”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> which typically includes values such as Spouse, Mother, and similar relationships.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the Application Form, under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Current/Communication Address section</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, the</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> fields Address 1, Address 2, and Address 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> typically contain address details such as Ashoka Society, Arera Colony, H. No. E7/112, Bhopal, or similar address information.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the Application Form, under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Current/Communication Address</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> section, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>the field</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“City”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> typically contains values such as </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Bhopal</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Indore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Lucknow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, and similar city names.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the Application Form, under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Current/Communication Address</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> section,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> the field</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Pincode”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> typically contains values such as </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>226024</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>110024</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>201010</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>400503</t>
     </r>
     <r>
@@ -2425,137 +2008,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>, and similar numeric codes.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the Application Form, under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Current/Communication Address</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> section, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>the field</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Mobile No.”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> typically contains values such as </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>8377998214</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>9876543210</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>7823445432</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, and other similar mobile numbers.</t>
     </r>
   </si>
   <si>
@@ -7776,158 +7228,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> section, the fields </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Office Address 1,” “Office Address 2,”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Office Address 3”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> typically contain address details such as </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Kishanganj Thana, Mhow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Indore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Madhya Pradesh</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>452001</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, and similar office address information.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the Application Form, under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Occupation/Business Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve"> section, the </t>
     </r>
     <r>
@@ -11563,6 +10863,704 @@
       </rPr>
       <t xml:space="preserve"> or similar comments. Extract and return the value exactly as it appears in the document without any modification, normalization, or interpretation.</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Basic Input</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sheet, navigate to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Proposed Loan Break-up”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> section and extract the value from the field </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Loan Amount.” Convert the extracted value into a pure numeric amount only, ensuring that all currency symbols and textual units such as Rs, INR, lakh, lacs, crore, etc. are removed. The final output must contain only digits, with no commas, spaces, or special characters (for example, Rs 30 lacs should be returned as 3000000).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Check the “Proposed Loan Break-up” section which will be in Tabular Form  and pick the value from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>field “Loan Amount.”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Convert the extracted value into a pure numeric amount only, ensuring that all currency symbols and textual units such as Rs, INR, lakh, lacs, crore, etc. are removed. The final output must contain only digits, with no commas, spaces, or special characters (for example, Rs 30 lacs should be returned as 3000000).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Loan Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> section, refer to the field </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Loan Amount Requested.”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Use the given value for mapping this PAS Field.
+Convert the extracted value into a pure numeric amount only, ensuring that all currency symbols and textual units such as Rs, INR, lakh, lacs, crore, etc. are removed. The final output must contain only digits, with no commas, spaces, or special characters (for example, Rs 30 lacs should be returned as 3000000).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The loan amount is typically mentioned in the Email Subject, such as </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Loan Amount – 15.00 Lacs,” “19 Lacs,”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">“Rs 30.00 Lacs.”, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>etc.
+Convert the extracted value into a pure numeric amount only, ensuring that all currency symbols and textual units such as Rs, INR, lakh, lacs, crore, etc. are removed. The final output must contain only digits, with no commas, spaces, or special characters (for example, Rs 30 lacs should be returned as 3000000).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the Application Form, under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Current/Communication Address section</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, the</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> fields Address 1, Address 2, and Address 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> typically contain address details such as Ashoka Society, Arera Colony, H. No. E7/112, Bhopal, or similar address information.
+While extracting the address, do not include commas (,) in the final output. If commas appear in the source value, remove them.
+Example:
+If Source: H. No. E7/112, Arera Colony, Bhopal
+then Output: H. No. E7/112 Arera Colony Bhopal</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the Application Form, under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Occupation/Business Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> section, the fields </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Office Address 1,” “Office Address 2,”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Office Address 3”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> typically contain address details such as </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kishanganj Thana, Mhow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Indore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Madhya Pradesh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>452001</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, and similar office address information.
+While extracting the address, do not include commas (,) in the final output. If commas appear in the source value, remove them.
+Example:
+if Source: H. No. E7/112, Arera Colony, Bhopal
+then Output: H. No. E7/112 Arera Colony Bhopal</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the Application Form, under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Current/Communication Address</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> section, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>the field</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Mobile No.”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> typically contains values such as </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+91 8377998214, +919876543210, 7823445432</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, and other similar mobile numbers.
+While extracting the mobile number, do not include the country code (+91). If the country code is present, remove it and return only the 10-digit mobile number.
+Example:
+Source: +91 8377998214
+Output: 8377998214</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Basic Input</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sheet under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Proposed Loan Break-up”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> section, extract the value from the field </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Proposed ROI.”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> This value is typically presented in formats like </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10.50%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12.00% etc.
+While extracting the value, do not include the percentage (%) sign. Remove the % symbol and return only the numeric value.
+Example:
+Source: 10.50%
+Output: 10.50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Proposed Loan Break-up” section</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> which will be tabular form, refer to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>field name “Proposed ROI,”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> where the value will appear in formats such as 10.50% or 12.00% etc
+While extracting the value, do not include the percentage (%) sign. Remove the % symbol and return only the numeric value.
+Example:
+Source: 10.50%
+Output: 10.50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>In the CAM file, under the AffordableCMAssessedIncome sheet, the</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> field “FOIR for Applied Loan Amount”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> typically contains values such as 44.55%, 33.24%, and similar percentages.
+While extracting the value, do not include the percentage (%) sign. Remove the % symbol and return only the numeric value.
+Example:
+Source: 10.50%
+Output: 10.50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the PD (Word document), under the Income Details section, which contains tabular data, the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>field “FOIR for Applied Loan Amount”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> typically includes values such as 55.02%, 33.24%, and similar percentages.
+While extracting the value, do not include the percentage (%) sign. Remove the % symbol and return only the numeric value.
+Example:
+Source: 10.50%
+Output: 10.50</t>
+    </r>
+  </si>
+  <si>
+    <t>Criticality</t>
   </si>
 </sst>
 </file>
@@ -12039,25 +12037,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3765008E-87C2-42DA-8C71-BC2650E30679}">
   <dimension ref="A1:N85"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.1328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1328125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.59765625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.265625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="30.1328125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="32.86328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="30.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="32.85546875" style="1" customWidth="1"/>
     <col min="9" max="9" width="34" style="1" customWidth="1"/>
-    <col min="10" max="10" width="31.86328125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="43.86328125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="21.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="33.265625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="43.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="21.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -12068,13 +12066,13 @@
         <v>99</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>126</v>
+        <v>253</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>129</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>130</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>1</v>
@@ -12101,7 +12099,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="4" customFormat="1" ht="84" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" s="4" customFormat="1" ht="96" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -12112,21 +12110,21 @@
         <v>30</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
@@ -12135,7 +12133,7 @@
       </c>
       <c r="N2" s="9"/>
     </row>
-    <row r="3" spans="1:14" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>10</v>
       </c>
@@ -12146,24 +12144,24 @@
         <v>25</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="J3" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
     </row>
-    <row r="4" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>11</v>
       </c>
@@ -12174,30 +12172,30 @@
         <v>25</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
       <c r="I4" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>135</v>
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
       <c r="M4" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N4" s="9"/>
     </row>
-    <row r="5" spans="1:14" ht="96" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
@@ -12208,13 +12206,13 @@
         <v>40</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -12231,7 +12229,7 @@
       </c>
       <c r="N5" s="9"/>
     </row>
-    <row r="6" spans="1:14" ht="48" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
@@ -12242,10 +12240,10 @@
         <v>50</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
@@ -12259,7 +12257,7 @@
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
     </row>
-    <row r="7" spans="1:14" ht="48" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" ht="144" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>14</v>
       </c>
@@ -12270,32 +12268,32 @@
         <v>20</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>137</v>
+        <v>242</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9" t="s">
-        <v>138</v>
+        <v>243</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>139</v>
+        <v>244</v>
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="9" t="s">
-        <v>140</v>
+        <v>245</v>
       </c>
       <c r="N7" s="9"/>
     </row>
-    <row r="8" spans="1:14" ht="48" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>15</v>
       </c>
@@ -12306,32 +12304,32 @@
         <v>3</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
       <c r="M8" s="9" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="N8" s="9"/>
     </row>
-    <row r="9" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14" ht="168" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>16</v>
       </c>
@@ -12342,20 +12340,20 @@
         <v>5</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>145</v>
+        <v>249</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
-        <v>146</v>
+        <v>250</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
@@ -12363,7 +12361,7 @@
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
     </row>
-    <row r="10" spans="1:14" ht="84" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14" ht="84" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>17</v>
       </c>
@@ -12374,30 +12372,30 @@
         <v>3</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
     </row>
-    <row r="11" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>18</v>
       </c>
@@ -12408,32 +12406,32 @@
         <v>2</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>109</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>110</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
     </row>
-    <row r="12" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14" ht="156" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>19</v>
       </c>
@@ -12444,22 +12442,22 @@
         <v>10</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>152</v>
+        <v>251</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>153</v>
+        <v>252</v>
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
@@ -12467,7 +12465,7 @@
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
     </row>
-    <row r="13" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>20</v>
       </c>
@@ -12478,28 +12476,28 @@
         <v>25</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
     </row>
-    <row r="14" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>21</v>
       </c>
@@ -12510,28 +12508,28 @@
         <v>25</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
       <c r="J14" s="9" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
       <c r="N14" s="9"/>
     </row>
-    <row r="15" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>22</v>
       </c>
@@ -12542,24 +12540,24 @@
         <v>8</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
       <c r="J15" s="9" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
     </row>
-    <row r="16" spans="1:14" ht="84" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>23</v>
       </c>
@@ -12570,19 +12568,19 @@
         <v>3</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
@@ -12591,7 +12589,7 @@
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
     </row>
-    <row r="17" spans="1:14" ht="72" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:14" ht="204" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>24</v>
       </c>
@@ -12602,24 +12600,24 @@
         <v>80</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9" t="s">
-        <v>158</v>
+        <v>246</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
       <c r="N17" s="9"/>
     </row>
-    <row r="18" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>25</v>
       </c>
@@ -12630,24 +12628,24 @@
         <v>25</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
       <c r="J18" s="9" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
     </row>
-    <row r="19" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>26</v>
       </c>
@@ -12658,24 +12656,24 @@
         <v>10</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
       <c r="J19" s="9" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
     </row>
-    <row r="20" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:14" ht="180" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>27</v>
       </c>
@@ -12686,24 +12684,24 @@
         <v>25</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
       <c r="J20" s="9" t="s">
-        <v>161</v>
+        <v>248</v>
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
       <c r="N20" s="9"/>
     </row>
-    <row r="21" spans="1:14" ht="24" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:14" ht="36" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>28</v>
       </c>
@@ -12714,13 +12712,13 @@
         <v>112</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="G21" s="9"/>
       <c r="H21" s="9" t="s">
@@ -12735,7 +12733,7 @@
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
     </row>
-    <row r="22" spans="1:14" ht="72" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>29</v>
       </c>
@@ -12746,30 +12744,30 @@
         <v>0</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
     </row>
-    <row r="23" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>30</v>
       </c>
@@ -12780,24 +12778,24 @@
         <v>40</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
       <c r="J23" s="9" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
       <c r="M23" s="9"/>
       <c r="N23" s="9"/>
     </row>
-    <row r="24" spans="1:14" ht="36" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:14" ht="36" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>31</v>
       </c>
@@ -12808,15 +12806,15 @@
         <v>0</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
@@ -12825,7 +12823,7 @@
       <c r="M24" s="9"/>
       <c r="N24" s="9"/>
     </row>
-    <row r="25" spans="1:14" ht="72" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>32</v>
       </c>
@@ -12836,30 +12834,30 @@
         <v>0</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G25" s="9"/>
       <c r="H25" s="9" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
     </row>
-    <row r="26" spans="1:14" ht="84" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>33</v>
       </c>
@@ -12870,14 +12868,14 @@
         <v>0</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="9" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
@@ -12887,7 +12885,7 @@
       <c r="M26" s="9"/>
       <c r="N26" s="9"/>
     </row>
-    <row r="27" spans="1:14" ht="84" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>34</v>
       </c>
@@ -12898,14 +12896,14 @@
         <v>0</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="9" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -12915,7 +12913,7 @@
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
     </row>
-    <row r="28" spans="1:14" ht="96" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:14" ht="108" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>35</v>
       </c>
@@ -12926,30 +12924,30 @@
         <v>22</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G28" s="9"/>
       <c r="H28" s="9" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
       <c r="N28" s="9"/>
     </row>
-    <row r="29" spans="1:14" ht="120" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:14" ht="132" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>36</v>
       </c>
@@ -12960,30 +12958,30 @@
         <v>0</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G29" s="9"/>
       <c r="H29" s="9" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
       <c r="M29" s="9"/>
       <c r="N29" s="9"/>
     </row>
-    <row r="30" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>37</v>
       </c>
@@ -12994,17 +12992,17 @@
         <v>0</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
@@ -13013,7 +13011,7 @@
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
     </row>
-    <row r="31" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>38</v>
       </c>
@@ -13024,17 +13022,17 @@
         <v>0</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="G31" s="9"/>
       <c r="H31" s="9" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
@@ -13043,7 +13041,7 @@
       <c r="M31" s="9"/>
       <c r="N31" s="9"/>
     </row>
-    <row r="32" spans="1:14" ht="96" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:14" ht="108" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>39</v>
       </c>
@@ -13054,20 +13052,20 @@
         <v>0</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H32" s="9"/>
       <c r="I32" s="11" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
@@ -13075,7 +13073,7 @@
       <c r="M32" s="9"/>
       <c r="N32" s="9"/>
     </row>
-    <row r="33" spans="1:14" ht="72" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>40</v>
       </c>
@@ -13086,20 +13084,20 @@
         <v>113</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="9" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -13107,7 +13105,7 @@
       <c r="M33" s="9"/>
       <c r="N33" s="9"/>
     </row>
-    <row r="34" spans="1:14" ht="36" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>41</v>
       </c>
@@ -13118,17 +13116,17 @@
         <v>3</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="9" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>123</v>
@@ -13139,7 +13137,7 @@
       <c r="M34" s="9"/>
       <c r="N34" s="9"/>
     </row>
-    <row r="35" spans="1:14" ht="120" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:14" ht="132" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>42</v>
       </c>
@@ -13150,16 +13148,16 @@
         <v>8</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
@@ -13169,7 +13167,7 @@
       <c r="M35" s="9"/>
       <c r="N35" s="9"/>
     </row>
-    <row r="36" spans="1:14" ht="156" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:14" ht="156" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>43</v>
       </c>
@@ -13180,13 +13178,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>124</v>
@@ -13199,7 +13197,7 @@
       <c r="M36" s="9"/>
       <c r="N36" s="9"/>
     </row>
-    <row r="37" spans="1:14" ht="120" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:14" ht="132" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>44</v>
       </c>
@@ -13210,16 +13208,16 @@
         <v>18</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
@@ -13229,7 +13227,7 @@
       <c r="M37" s="9"/>
       <c r="N37" s="9"/>
     </row>
-    <row r="38" spans="1:14" ht="108" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:14" ht="132" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>45</v>
       </c>
@@ -13240,16 +13238,16 @@
         <v>18</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
@@ -13259,7 +13257,7 @@
       <c r="M38" s="9"/>
       <c r="N38" s="9"/>
     </row>
-    <row r="39" spans="1:14" ht="108" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:14" ht="120" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>46</v>
       </c>
@@ -13270,16 +13268,16 @@
         <v>18</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
@@ -13289,7 +13287,7 @@
       <c r="M39" s="9"/>
       <c r="N39" s="9"/>
     </row>
-    <row r="40" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>47</v>
       </c>
@@ -13300,28 +13298,28 @@
         <v>20</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
       <c r="J40" s="9" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="K40" s="9"/>
       <c r="L40" s="9"/>
       <c r="M40" s="9"/>
       <c r="N40" s="9"/>
     </row>
-    <row r="41" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>48</v>
       </c>
@@ -13332,14 +13330,14 @@
         <v>114</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="11" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
@@ -13349,7 +13347,7 @@
       <c r="M41" s="9"/>
       <c r="N41" s="9"/>
     </row>
-    <row r="42" spans="1:14" ht="72" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:14" ht="84" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>49</v>
       </c>
@@ -13360,14 +13358,14 @@
         <v>114</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F42" s="8"/>
       <c r="G42" s="9" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
@@ -13377,7 +13375,7 @@
       <c r="M42" s="9"/>
       <c r="N42" s="9"/>
     </row>
-    <row r="43" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>50</v>
       </c>
@@ -13388,19 +13386,19 @@
         <v>115</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="9"/>
@@ -13409,7 +13407,7 @@
       <c r="M43" s="9"/>
       <c r="N43" s="9"/>
     </row>
-    <row r="44" spans="1:14" ht="48" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>51</v>
       </c>
@@ -13420,16 +13418,16 @@
         <v>115</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
@@ -13439,7 +13437,7 @@
       <c r="M44" s="9"/>
       <c r="N44" s="9"/>
     </row>
-    <row r="45" spans="1:14" ht="48" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>52</v>
       </c>
@@ -13450,14 +13448,14 @@
         <v>115</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F45" s="8"/>
       <c r="G45" s="9" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
@@ -13467,7 +13465,7 @@
       <c r="M45" s="9"/>
       <c r="N45" s="9"/>
     </row>
-    <row r="46" spans="1:14" ht="48" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>53</v>
       </c>
@@ -13478,10 +13476,10 @@
         <v>0</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
@@ -13489,13 +13487,13 @@
       <c r="I46" s="9"/>
       <c r="J46" s="9"/>
       <c r="K46" s="9" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="L46" s="9"/>
       <c r="M46" s="9"/>
       <c r="N46" s="9"/>
     </row>
-    <row r="47" spans="1:14" ht="84" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:14" ht="84" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>54</v>
       </c>
@@ -13506,14 +13504,14 @@
         <v>0</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="9" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
@@ -13523,7 +13521,7 @@
       <c r="M47" s="9"/>
       <c r="N47" s="9"/>
     </row>
-    <row r="48" spans="1:14" ht="84" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:14" ht="84" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>55</v>
       </c>
@@ -13534,14 +13532,14 @@
         <v>114</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F48" s="8"/>
       <c r="G48" s="9" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="H48" s="9"/>
       <c r="I48" s="9"/>
@@ -13551,7 +13549,7 @@
       <c r="M48" s="9"/>
       <c r="N48" s="9"/>
     </row>
-    <row r="49" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>56</v>
       </c>
@@ -13562,16 +13560,16 @@
         <v>116</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
@@ -13581,7 +13579,7 @@
       <c r="M49" s="9"/>
       <c r="N49" s="9"/>
     </row>
-    <row r="50" spans="1:14" ht="132" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:14" ht="132" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>57</v>
       </c>
@@ -13592,26 +13590,26 @@
         <v>500</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
       <c r="I50" s="9"/>
       <c r="J50" s="9"/>
       <c r="K50" s="9" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="L50" s="9"/>
       <c r="M50" s="9"/>
       <c r="N50" s="9"/>
     </row>
-    <row r="51" spans="1:14" ht="24" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:14" ht="24" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>58</v>
       </c>
@@ -13622,10 +13620,10 @@
         <v>0</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="F51" s="8"/>
       <c r="G51" s="9"/>
@@ -13633,13 +13631,13 @@
       <c r="I51" s="9"/>
       <c r="J51" s="9"/>
       <c r="K51" s="9" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="L51" s="9"/>
       <c r="M51" s="9"/>
       <c r="N51" s="9"/>
     </row>
-    <row r="52" spans="1:14" ht="48" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
         <v>59</v>
       </c>
@@ -13650,13 +13648,13 @@
         <v>107</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G52" s="9"/>
       <c r="H52" s="9" t="s">
@@ -13671,7 +13669,7 @@
       <c r="M52" s="9"/>
       <c r="N52" s="9"/>
     </row>
-    <row r="53" spans="1:14" ht="36" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:14" ht="36" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
         <v>60</v>
       </c>
@@ -13682,24 +13680,24 @@
         <v>107</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F53" s="8"/>
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
       <c r="I53" s="9"/>
       <c r="J53" s="9" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="K53" s="9"/>
       <c r="L53" s="9"/>
       <c r="M53" s="9"/>
       <c r="N53" s="9"/>
     </row>
-    <row r="54" spans="1:14" ht="108" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:14" ht="108" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>61</v>
       </c>
@@ -13710,30 +13708,30 @@
         <v>113</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G54" s="9"/>
       <c r="H54" s="9" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="K54" s="9"/>
       <c r="L54" s="9"/>
       <c r="M54" s="9"/>
       <c r="N54" s="9"/>
     </row>
-    <row r="55" spans="1:14" ht="84" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
         <v>62</v>
       </c>
@@ -13744,30 +13742,30 @@
         <v>118</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G55" s="9"/>
       <c r="H55" s="9" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="K55" s="9"/>
       <c r="L55" s="9"/>
       <c r="M55" s="9"/>
       <c r="N55" s="9"/>
     </row>
-    <row r="56" spans="1:14" ht="96" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:14" ht="108" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>63</v>
       </c>
@@ -13778,18 +13776,18 @@
         <v>119</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F56" s="8"/>
       <c r="G56" s="9"/>
       <c r="H56" s="9" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="J56" s="9"/>
       <c r="K56" s="9"/>
@@ -13797,7 +13795,7 @@
       <c r="M56" s="9"/>
       <c r="N56" s="9"/>
     </row>
-    <row r="57" spans="1:14" ht="48" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:14" ht="48" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>64</v>
       </c>
@@ -13808,28 +13806,28 @@
         <v>107</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G57" s="9"/>
       <c r="H57" s="9" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="9" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="K57" s="9"/>
       <c r="L57" s="9"/>
       <c r="M57" s="9"/>
       <c r="N57" s="9"/>
     </row>
-    <row r="58" spans="1:14" ht="120" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:14" ht="144" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>65</v>
       </c>
@@ -13840,30 +13838,30 @@
         <v>118</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G58" s="9"/>
       <c r="H58" s="9" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="K58" s="9"/>
       <c r="L58" s="9"/>
       <c r="M58" s="9"/>
       <c r="N58" s="9"/>
     </row>
-    <row r="59" spans="1:14" ht="144" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:14" ht="144" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
         <v>66</v>
       </c>
@@ -13874,30 +13872,30 @@
         <v>118</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G59" s="9"/>
       <c r="H59" s="9" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="K59" s="9"/>
       <c r="L59" s="9"/>
       <c r="M59" s="9"/>
       <c r="N59" s="9"/>
     </row>
-    <row r="60" spans="1:14" ht="84" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:14" ht="216" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>67</v>
       </c>
@@ -13908,24 +13906,24 @@
         <v>80</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F60" s="8"/>
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
       <c r="I60" s="9"/>
       <c r="J60" s="9" t="s">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="K60" s="9"/>
       <c r="L60" s="9"/>
       <c r="M60" s="9"/>
       <c r="N60" s="9"/>
     </row>
-    <row r="61" spans="1:14" ht="48" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>68</v>
       </c>
@@ -13936,24 +13934,24 @@
         <v>80</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F61" s="8"/>
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
       <c r="I61" s="9"/>
       <c r="J61" s="9" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="K61" s="9"/>
       <c r="L61" s="9"/>
       <c r="M61" s="9"/>
       <c r="N61" s="9"/>
     </row>
-    <row r="62" spans="1:14" ht="72" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
         <v>69</v>
       </c>
@@ -13964,14 +13962,14 @@
         <v>113</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F62" s="8"/>
       <c r="G62" s="9" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="H62" s="9"/>
       <c r="I62" s="9"/>
@@ -13981,7 +13979,7 @@
       <c r="M62" s="9"/>
       <c r="N62" s="9"/>
     </row>
-    <row r="63" spans="1:14" ht="132" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:14" ht="132" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
         <v>70</v>
       </c>
@@ -13992,17 +13990,17 @@
         <v>3</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="G63" s="9"/>
       <c r="H63" s="11" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="9"/>
@@ -14011,7 +14009,7 @@
       <c r="M63" s="9"/>
       <c r="N63" s="9"/>
     </row>
-    <row r="64" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>71</v>
       </c>
@@ -14022,16 +14020,16 @@
         <v>117</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="H64" s="9"/>
       <c r="I64" s="9"/>
@@ -14041,7 +14039,7 @@
       <c r="M64" s="9"/>
       <c r="N64" s="9"/>
     </row>
-    <row r="65" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>72</v>
       </c>
@@ -14052,16 +14050,16 @@
         <v>120</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="H65" s="9"/>
       <c r="I65" s="9"/>
@@ -14071,7 +14069,7 @@
       <c r="M65" s="9"/>
       <c r="N65" s="9"/>
     </row>
-    <row r="66" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
         <v>73</v>
       </c>
@@ -14082,16 +14080,16 @@
         <v>120</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="H66" s="9"/>
       <c r="I66" s="9"/>
@@ -14101,7 +14099,7 @@
       <c r="M66" s="9"/>
       <c r="N66" s="9"/>
     </row>
-    <row r="67" spans="1:14" ht="72" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:14" ht="84" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
         <v>74</v>
       </c>
@@ -14112,16 +14110,16 @@
         <v>121</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="H67" s="9"/>
       <c r="I67" s="9"/>
@@ -14131,7 +14129,7 @@
       <c r="M67" s="9"/>
       <c r="N67" s="9"/>
     </row>
-    <row r="68" spans="1:14" ht="72" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
         <v>75</v>
       </c>
@@ -14142,16 +14140,16 @@
         <v>18</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H68" s="9"/>
       <c r="I68" s="9"/>
@@ -14161,7 +14159,7 @@
       <c r="M68" s="9"/>
       <c r="N68" s="9"/>
     </row>
-    <row r="69" spans="1:14" ht="72" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
         <v>76</v>
       </c>
@@ -14172,16 +14170,16 @@
         <v>121</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="H69" s="9"/>
       <c r="I69" s="9"/>
@@ -14191,7 +14189,7 @@
       <c r="M69" s="9"/>
       <c r="N69" s="9"/>
     </row>
-    <row r="70" spans="1:14" ht="96" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:14" ht="108" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
         <v>77</v>
       </c>
@@ -14202,16 +14200,16 @@
         <v>18</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="H70" s="9"/>
       <c r="I70" s="9"/>
@@ -14221,7 +14219,7 @@
       <c r="M70" s="9"/>
       <c r="N70" s="9"/>
     </row>
-    <row r="71" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
         <v>78</v>
       </c>
@@ -14232,16 +14230,16 @@
         <v>121</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="H71" s="9"/>
       <c r="I71" s="9"/>
@@ -14251,7 +14249,7 @@
       <c r="M71" s="9"/>
       <c r="N71" s="9"/>
     </row>
-    <row r="72" spans="1:14" ht="48" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
         <v>79</v>
       </c>
@@ -14262,16 +14260,16 @@
         <v>16</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="H72" s="9"/>
       <c r="I72" s="9"/>
@@ -14281,7 +14279,7 @@
       <c r="M72" s="9"/>
       <c r="N72" s="9"/>
     </row>
-    <row r="73" spans="1:14" ht="48" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
         <v>80</v>
       </c>
@@ -14292,16 +14290,16 @@
         <v>120</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="H73" s="9"/>
       <c r="I73" s="9"/>
@@ -14311,7 +14309,7 @@
       <c r="M73" s="9"/>
       <c r="N73" s="9"/>
     </row>
-    <row r="74" spans="1:14" ht="72" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
         <v>81</v>
       </c>
@@ -14322,16 +14320,16 @@
         <v>18</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="H74" s="9"/>
       <c r="I74" s="9"/>
@@ -14341,7 +14339,7 @@
       <c r="M74" s="9"/>
       <c r="N74" s="9"/>
     </row>
-    <row r="75" spans="1:14" ht="72" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:14" ht="84" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
         <v>82</v>
       </c>
@@ -14352,16 +14350,16 @@
         <v>16</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="H75" s="9"/>
       <c r="I75" s="9"/>
@@ -14371,7 +14369,7 @@
       <c r="M75" s="9"/>
       <c r="N75" s="9"/>
     </row>
-    <row r="76" spans="1:14" ht="84" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
         <v>83</v>
       </c>
@@ -14382,16 +14380,16 @@
         <v>18</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="H76" s="9"/>
       <c r="I76" s="9"/>
@@ -14401,7 +14399,7 @@
       <c r="M76" s="9"/>
       <c r="N76" s="9"/>
     </row>
-    <row r="77" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
         <v>84</v>
       </c>
@@ -14412,16 +14410,16 @@
         <v>122</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="H77" s="9"/>
       <c r="I77" s="9"/>
@@ -14431,7 +14429,7 @@
       <c r="M77" s="9"/>
       <c r="N77" s="9"/>
     </row>
-    <row r="78" spans="1:14" ht="84" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:14" ht="84" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
         <v>85</v>
       </c>
@@ -14442,14 +14440,14 @@
         <v>114</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F78" s="8"/>
       <c r="G78" s="9" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="H78" s="9"/>
       <c r="I78" s="9"/>
@@ -14459,7 +14457,7 @@
       <c r="M78" s="9"/>
       <c r="N78" s="9"/>
     </row>
-    <row r="79" spans="1:14" ht="84" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:14" ht="84" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
         <v>86</v>
       </c>
@@ -14470,14 +14468,14 @@
         <v>0</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F79" s="8"/>
       <c r="G79" s="9" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="H79" s="9"/>
       <c r="I79" s="9"/>
@@ -14487,7 +14485,7 @@
       <c r="M79" s="9"/>
       <c r="N79" s="9"/>
     </row>
-    <row r="80" spans="1:14" ht="60" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:14" ht="72" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
         <v>87</v>
       </c>
@@ -14498,14 +14496,14 @@
         <v>20</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F80" s="8"/>
       <c r="G80" s="9" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="H80" s="9"/>
       <c r="I80" s="9"/>
@@ -14515,7 +14513,7 @@
       <c r="M80" s="9"/>
       <c r="N80" s="9"/>
     </row>
-    <row r="81" spans="1:14" ht="72" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:14" ht="84" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
         <v>88</v>
       </c>
@@ -14526,14 +14524,14 @@
         <v>0</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F81" s="8"/>
       <c r="G81" s="9" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H81" s="9"/>
       <c r="I81" s="9"/>
@@ -14543,7 +14541,7 @@
       <c r="M81" s="9"/>
       <c r="N81" s="9"/>
     </row>
-    <row r="82" spans="1:14" ht="72" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:14" ht="84" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
         <v>89</v>
       </c>
@@ -14554,20 +14552,20 @@
         <v>121</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="H82" s="9"/>
       <c r="I82" s="9" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="J82" s="9"/>
       <c r="K82" s="9"/>
@@ -14575,7 +14573,7 @@
       <c r="M82" s="9"/>
       <c r="N82" s="9"/>
     </row>
-    <row r="83" spans="1:14" ht="84" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
         <v>90</v>
       </c>
@@ -14586,16 +14584,16 @@
         <v>18</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="H83" s="9"/>
       <c r="I83" s="9"/>
@@ -14605,7 +14603,7 @@
       <c r="M83" s="9"/>
       <c r="N83" s="9"/>
     </row>
-    <row r="84" spans="1:14" ht="84" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:14" ht="96" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
         <v>91</v>
       </c>
@@ -14616,16 +14614,16 @@
         <v>18</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="H84" s="9"/>
       <c r="I84" s="9"/>
@@ -14635,7 +14633,7 @@
       <c r="M84" s="9"/>
       <c r="N84" s="9"/>
     </row>
-    <row r="85" spans="1:14" ht="96" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:14" ht="108" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
         <v>92</v>
       </c>
@@ -14646,16 +14644,16 @@
         <v>18</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="H85" s="9"/>
       <c r="I85" s="9"/>

--- a/FieldConfigrationFile.xlsx
+++ b/FieldConfigrationFile.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P_Singh07\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prakhar\Desktop\Projects\IMGC Project\Field Level Mapping Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FD32C5A-B07C-4D86-A961-FC517DD9948D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A3031AA-6E47-4198-986A-0FB39D6DE122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="3855" windowWidth="21600" windowHeight="11385" xr2:uid="{02CFE6FC-DC13-4DF7-B179-54CE07624848}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{02CFE6FC-DC13-4DF7-B179-54CE07624848}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -11045,6 +11045,9 @@
     </r>
   </si>
   <si>
+    <t>Mismatch Criticality</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">In the Application Form, under the </t>
     </r>
@@ -11558,9 +11561,6 @@
 Source: 10.50%
 Output: 10.50</t>
     </r>
-  </si>
-  <si>
-    <t>Criticality</t>
   </si>
 </sst>
 </file>
@@ -12066,7 +12066,7 @@
         <v>99</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>128</v>
@@ -12349,11 +12349,11 @@
         <v>231</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
@@ -12451,13 +12451,13 @@
         <v>231</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>234</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
@@ -12610,7 +12610,7 @@
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
@@ -12694,7 +12694,7 @@
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
       <c r="J20" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
@@ -13916,7 +13916,7 @@
       <c r="H60" s="9"/>
       <c r="I60" s="9"/>
       <c r="J60" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K60" s="9"/>
       <c r="L60" s="9"/>

--- a/FieldConfigrationFile.xlsx
+++ b/FieldConfigrationFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prakhar\Desktop\Projects\IMGC Project\Field Level Mapping Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A3031AA-6E47-4198-986A-0FB39D6DE122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BB69C3-250F-419D-A0F4-8ED933AA2ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{02CFE6FC-DC13-4DF7-B179-54CE07624848}"/>
   </bookViews>
@@ -760,195 +760,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">In the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Basic Input</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sheet of the CAM Excel, go to the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Proposed Loan Break-up”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> section and pick the value from the field </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Tenure (Months).”</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In the tabular section titled </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Proposed Loan Break-up,”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> extract the value from the field </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Tenure (Months).”</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Loan Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> section, use the value from the field </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Loan Tenure (Months)”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> for mapping this PAS Field.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The tenure is usually mentioned in the Email Subject, such as </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“240 Months”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> or </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>“Tenure – 240 Months”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> etc.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">In the CAM Excel file, within the </t>
     </r>
     <r>
@@ -11560,6 +11371,224 @@
 Example:
 Source: 10.50%
 Output: 10.50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Basic Input</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sheet of the CAM Excel, go to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Proposed Loan Break-up”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> section and pick the value from the field </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Tenure (Months).”
+This field may contain values such as 240 Months, 240, 198 months, or similar formats.
+While extracting the value, return only the numeric digits. Do not include any text such as “Months” or “months” in the final output.
+Example:
+Source: 198 months
+Output: 198</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In the tabular section titled </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Proposed Loan Break-up,”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> extract the value from the field </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Tenure (Months).”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> This field may contain values such as 240 Months, 240, 198 months, or similar formats.
+While extracting the value, return only the numeric digits. Do not include any text such as “Months” or “months” in the final output.
+Example:
+Source: 198 months
+Output: 198</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Loan Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> section, use the value from the field </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Loan Tenure (Months)”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for mapping this PAS Field.
+This field may contain values such as 240 Months, 240, 198 months, or similar formats.
+While extracting the value, return only the numeric digits. Do not include any text such as “Months” or “months” in the final output.
+Example:
+Source: 198 months
+Output: 198</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The tenure is usually mentioned in the Email Subject, such as </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“240 Months”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>“Tenure – 240 Months”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> etc.
+This field may contain values such as 240 Months, 240, 198 months, or similar formats.
+While extracting the value, return only the numeric digits. Do not include any text such as “Months” or “months” in the final output.
+Example:
+Source: 198 months
+Output: 198</t>
     </r>
   </si>
 </sst>
@@ -12066,7 +12095,7 @@
         <v>99</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>128</v>
@@ -12113,10 +12142,10 @@
         <v>126</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
@@ -12147,7 +12176,7 @@
         <v>126</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="9"/>
@@ -12175,10 +12204,10 @@
         <v>126</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
@@ -12209,10 +12238,10 @@
         <v>126</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -12243,7 +12272,7 @@
         <v>126</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
@@ -12271,29 +12300,29 @@
         <v>126</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="9" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="N7" s="9"/>
     </row>
-    <row r="8" spans="1:14" ht="48" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="192" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>15</v>
       </c>
@@ -12307,25 +12336,25 @@
         <v>126</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>136</v>
+        <v>250</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9" t="s">
-        <v>137</v>
+        <v>251</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>138</v>
+        <v>252</v>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
       <c r="M8" s="9" t="s">
-        <v>139</v>
+        <v>253</v>
       </c>
       <c r="N8" s="9"/>
     </row>
@@ -12343,17 +12372,17 @@
         <v>126</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
@@ -12375,20 +12404,20 @@
         <v>126</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
@@ -12409,22 +12438,22 @@
         <v>126</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>109</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>110</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
@@ -12445,19 +12474,19 @@
         <v>126</v>
       </c>
       <c r="E12" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>234</v>
-      </c>
       <c r="I12" s="9" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
@@ -12479,18 +12508,18 @@
         <v>126</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
@@ -12511,18 +12540,18 @@
         <v>126</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
       <c r="J14" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
@@ -12543,14 +12572,14 @@
         <v>126</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
       <c r="J15" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
@@ -12571,16 +12600,16 @@
         <v>126</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F16" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="G16" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="G16" s="9" t="s">
-        <v>235</v>
-      </c>
       <c r="H16" s="9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
@@ -12603,14 +12632,14 @@
         <v>127</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
@@ -12631,14 +12660,14 @@
         <v>126</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
       <c r="J18" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
@@ -12659,14 +12688,14 @@
         <v>126</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
       <c r="J19" s="9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
@@ -12687,14 +12716,14 @@
         <v>126</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
       <c r="J20" s="9" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
@@ -12715,10 +12744,10 @@
         <v>126</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G21" s="9"/>
       <c r="H21" s="9" t="s">
@@ -12747,20 +12776,20 @@
         <v>126</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
@@ -12781,14 +12810,14 @@
         <v>126</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
       <c r="J23" s="9" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
@@ -12809,12 +12838,12 @@
         <v>127</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
@@ -12837,20 +12866,20 @@
         <v>127</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G25" s="9"/>
       <c r="H25" s="9" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
@@ -12871,11 +12900,11 @@
         <v>126</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
@@ -12899,11 +12928,11 @@
         <v>126</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -12927,20 +12956,20 @@
         <v>126</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G28" s="9"/>
       <c r="H28" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
@@ -12961,20 +12990,20 @@
         <v>126</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G29" s="9"/>
       <c r="H29" s="9" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
@@ -12995,14 +13024,14 @@
         <v>127</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
@@ -13025,14 +13054,14 @@
         <v>126</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G31" s="9"/>
       <c r="H31" s="9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
@@ -13055,17 +13084,17 @@
         <v>127</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H32" s="9"/>
       <c r="I32" s="11" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
@@ -13087,17 +13116,17 @@
         <v>127</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="9" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -13119,14 +13148,14 @@
         <v>126</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>123</v>
@@ -13151,13 +13180,13 @@
         <v>127</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
@@ -13181,10 +13210,10 @@
         <v>127</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>124</v>
@@ -13211,13 +13240,13 @@
         <v>127</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
@@ -13241,13 +13270,13 @@
         <v>127</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
@@ -13271,13 +13300,13 @@
         <v>127</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
@@ -13301,18 +13330,18 @@
         <v>126</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
       <c r="J40" s="9" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="K40" s="9"/>
       <c r="L40" s="9"/>
@@ -13333,11 +13362,11 @@
         <v>126</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="11" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
@@ -13361,11 +13390,11 @@
         <v>127</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F42" s="8"/>
       <c r="G42" s="9" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
@@ -13389,16 +13418,16 @@
         <v>126</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="9"/>
@@ -13421,13 +13450,13 @@
         <v>126</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
@@ -13451,11 +13480,11 @@
         <v>126</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F45" s="8"/>
       <c r="G45" s="9" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
@@ -13479,7 +13508,7 @@
         <v>126</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
@@ -13487,7 +13516,7 @@
       <c r="I46" s="9"/>
       <c r="J46" s="9"/>
       <c r="K46" s="9" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L46" s="9"/>
       <c r="M46" s="9"/>
@@ -13507,11 +13536,11 @@
         <v>127</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
@@ -13535,11 +13564,11 @@
         <v>127</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F48" s="8"/>
       <c r="G48" s="9" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H48" s="9"/>
       <c r="I48" s="9"/>
@@ -13563,13 +13592,13 @@
         <v>126</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
@@ -13593,17 +13622,17 @@
         <v>127</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
       <c r="I50" s="9"/>
       <c r="J50" s="9"/>
       <c r="K50" s="9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="L50" s="9"/>
       <c r="M50" s="9"/>
@@ -13623,7 +13652,7 @@
         <v>126</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F51" s="8"/>
       <c r="G51" s="9"/>
@@ -13631,7 +13660,7 @@
       <c r="I51" s="9"/>
       <c r="J51" s="9"/>
       <c r="K51" s="9" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L51" s="9"/>
       <c r="M51" s="9"/>
@@ -13651,10 +13680,10 @@
         <v>126</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G52" s="9"/>
       <c r="H52" s="9" t="s">
@@ -13683,14 +13712,14 @@
         <v>126</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F53" s="8"/>
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
       <c r="I53" s="9"/>
       <c r="J53" s="9" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="K53" s="9"/>
       <c r="L53" s="9"/>
@@ -13711,20 +13740,20 @@
         <v>126</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G54" s="9"/>
       <c r="H54" s="9" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="K54" s="9"/>
       <c r="L54" s="9"/>
@@ -13745,20 +13774,20 @@
         <v>127</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G55" s="9"/>
       <c r="H55" s="9" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K55" s="9"/>
       <c r="L55" s="9"/>
@@ -13779,15 +13808,15 @@
         <v>126</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F56" s="8"/>
       <c r="G56" s="9"/>
       <c r="H56" s="9" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="J56" s="9"/>
       <c r="K56" s="9"/>
@@ -13809,18 +13838,18 @@
         <v>126</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G57" s="9"/>
       <c r="H57" s="9" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="9" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K57" s="9"/>
       <c r="L57" s="9"/>
@@ -13841,20 +13870,20 @@
         <v>126</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G58" s="9"/>
       <c r="H58" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K58" s="9"/>
       <c r="L58" s="9"/>
@@ -13875,20 +13904,20 @@
         <v>126</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G59" s="9"/>
       <c r="H59" s="9" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="K59" s="9"/>
       <c r="L59" s="9"/>
@@ -13909,14 +13938,14 @@
         <v>127</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F60" s="8"/>
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
       <c r="I60" s="9"/>
       <c r="J60" s="9" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="K60" s="9"/>
       <c r="L60" s="9"/>
@@ -13937,14 +13966,14 @@
         <v>127</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F61" s="8"/>
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
       <c r="I61" s="9"/>
       <c r="J61" s="9" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="K61" s="9"/>
       <c r="L61" s="9"/>
@@ -13965,11 +13994,11 @@
         <v>127</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F62" s="8"/>
       <c r="G62" s="9" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H62" s="9"/>
       <c r="I62" s="9"/>
@@ -13993,14 +14022,14 @@
         <v>127</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G63" s="9"/>
       <c r="H63" s="11" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="9"/>
@@ -14023,13 +14052,13 @@
         <v>127</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H64" s="9"/>
       <c r="I64" s="9"/>
@@ -14053,13 +14082,13 @@
         <v>126</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H65" s="9"/>
       <c r="I65" s="9"/>
@@ -14083,13 +14112,13 @@
         <v>126</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H66" s="9"/>
       <c r="I66" s="9"/>
@@ -14113,13 +14142,13 @@
         <v>126</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H67" s="9"/>
       <c r="I67" s="9"/>
@@ -14143,13 +14172,13 @@
         <v>126</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H68" s="9"/>
       <c r="I68" s="9"/>
@@ -14173,13 +14202,13 @@
         <v>126</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H69" s="9"/>
       <c r="I69" s="9"/>
@@ -14203,13 +14232,13 @@
         <v>127</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H70" s="9"/>
       <c r="I70" s="9"/>
@@ -14233,13 +14262,13 @@
         <v>127</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H71" s="9"/>
       <c r="I71" s="9"/>
@@ -14263,13 +14292,13 @@
         <v>127</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H72" s="9"/>
       <c r="I72" s="9"/>
@@ -14293,13 +14322,13 @@
         <v>127</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H73" s="9"/>
       <c r="I73" s="9"/>
@@ -14323,13 +14352,13 @@
         <v>126</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="H74" s="9"/>
       <c r="I74" s="9"/>
@@ -14353,13 +14382,13 @@
         <v>126</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H75" s="9"/>
       <c r="I75" s="9"/>
@@ -14383,13 +14412,13 @@
         <v>127</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H76" s="9"/>
       <c r="I76" s="9"/>
@@ -14413,13 +14442,13 @@
         <v>127</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H77" s="9"/>
       <c r="I77" s="9"/>
@@ -14443,11 +14472,11 @@
         <v>127</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F78" s="8"/>
       <c r="G78" s="9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="H78" s="9"/>
       <c r="I78" s="9"/>
@@ -14471,11 +14500,11 @@
         <v>127</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F79" s="8"/>
       <c r="G79" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="H79" s="9"/>
       <c r="I79" s="9"/>
@@ -14499,11 +14528,11 @@
         <v>127</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F80" s="8"/>
       <c r="G80" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="H80" s="9"/>
       <c r="I80" s="9"/>
@@ -14527,11 +14556,11 @@
         <v>127</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F81" s="8"/>
       <c r="G81" s="9" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="H81" s="9"/>
       <c r="I81" s="9"/>
@@ -14555,17 +14584,17 @@
         <v>127</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H82" s="9"/>
       <c r="I82" s="9" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="J82" s="9"/>
       <c r="K82" s="9"/>
@@ -14587,13 +14616,13 @@
         <v>127</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="H83" s="9"/>
       <c r="I83" s="9"/>
@@ -14617,13 +14646,13 @@
         <v>127</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H84" s="9"/>
       <c r="I84" s="9"/>
@@ -14647,13 +14676,13 @@
         <v>127</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="H85" s="9"/>
       <c r="I85" s="9"/>
